--- a/data/top_ten_imp_wt.xlsx
+++ b/data/top_ten_imp_wt.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,10 +362,15 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>total_weight</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -378,9 +383,12 @@
         </is>
       </c>
       <c r="B2">
-        <v>12838.572134</v>
-      </c>
-      <c r="C2" t="inlineStr">
+        <v>2022</v>
+      </c>
+      <c r="C2">
+        <v>17264.980101</v>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>Natural gas and other fossil products</t>
         </is>
@@ -389,133 +397,1420 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B3">
-        <v>4646.688523</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Other foodstuffs</t>
+        <v>2021</v>
+      </c>
+      <c r="C3">
+        <v>17220.743499</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Natural gas and other fossil products</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B4">
-        <v>4350.039765</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Nonmetal min. prods.</t>
+        <v>2023</v>
+      </c>
+      <c r="C4">
+        <v>16258.640772</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Natural gas and other fossil products</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B5">
-        <v>3990.295378</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Mixed freight</t>
+        <v>2018</v>
+      </c>
+      <c r="C5">
+        <v>15894.940824</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Natural gas and other fossil products</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B6">
-        <v>2485.283781</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Basic chemicals</t>
+        <v>2019</v>
+      </c>
+      <c r="C6">
+        <v>15708.159782</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Natural gas and other fossil products</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B7">
-        <v>2376.516354</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Fuel oils</t>
+        <v>2024</v>
+      </c>
+      <c r="C7">
+        <v>14955.16099</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Natural gas and other fossil products</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B8">
-        <v>2195.577746</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Wood prods.</t>
+        <v>2020</v>
+      </c>
+      <c r="C8">
+        <v>14496.223408</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Natural gas and other fossil products</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B9">
-        <v>1963.954715</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Plastics/rubber</t>
+        <v>2017</v>
+      </c>
+      <c r="C9">
+        <v>12838.572134</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Natural gas and other fossil products</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>07</t>
         </is>
       </c>
       <c r="B10">
-        <v>1768.670449</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Base metals</t>
+        <v>2017</v>
+      </c>
+      <c r="C10">
+        <v>4646.688523</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Other foodstuffs</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>2022</v>
+      </c>
+      <c r="C11">
+        <v>4579.652123</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Other foodstuffs</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>2018</v>
+      </c>
+      <c r="C12">
+        <v>4535.967545</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Nonmetal min. prods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>2018</v>
+      </c>
+      <c r="C13">
+        <v>4518.224425</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Other foodstuffs</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>2024</v>
+      </c>
+      <c r="C14">
+        <v>4516.274485</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Other foodstuffs</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>2023</v>
+      </c>
+      <c r="C15">
+        <v>4515.561965</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Other foodstuffs</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>2019</v>
+      </c>
+      <c r="C16">
+        <v>4499.754873</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Other foodstuffs</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>2021</v>
+      </c>
+      <c r="C17">
+        <v>4491.324813</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Other foodstuffs</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>2020</v>
+      </c>
+      <c r="C18">
+        <v>4485.359804</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Other foodstuffs</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>2019</v>
+      </c>
+      <c r="C19">
+        <v>4457.371776</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Nonmetal min. prods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>2020</v>
+      </c>
+      <c r="C20">
+        <v>4412.877439</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Nonmetal min. prods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>2021</v>
+      </c>
+      <c r="C21">
+        <v>4378.264094</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Nonmetal min. prods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>2017</v>
+      </c>
+      <c r="C22">
+        <v>4350.039765</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Nonmetal min. prods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>2022</v>
+      </c>
+      <c r="C23">
+        <v>4249.406888</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Nonmetal min. prods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>2024</v>
+      </c>
+      <c r="C24">
+        <v>4021.355547</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Nonmetal min. prods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>2017</v>
+      </c>
+      <c r="C25">
+        <v>3990.295378</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Mixed freight</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>2023</v>
+      </c>
+      <c r="C26">
+        <v>3923.150867</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Nonmetal min. prods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>2018</v>
+      </c>
+      <c r="C27">
+        <v>3880.192673</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Mixed freight</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>2019</v>
+      </c>
+      <c r="C28">
+        <v>3815.577596</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Mixed freight</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>2021</v>
+      </c>
+      <c r="C29">
+        <v>3795.928877</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Mixed freight</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>2020</v>
+      </c>
+      <c r="C30">
+        <v>3788.691839</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Mixed freight</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>2023</v>
+      </c>
+      <c r="C31">
+        <v>3738.213285</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Mixed freight</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>2024</v>
+      </c>
+      <c r="C32">
+        <v>3727.651679</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Mixed freight</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>2022</v>
+      </c>
+      <c r="C33">
+        <v>3712.617242</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Mixed freight</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B11">
+      <c r="B34">
+        <v>2024</v>
+      </c>
+      <c r="C34">
+        <v>3313.469635</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Gasoline</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>2017</v>
+      </c>
+      <c r="C35">
+        <v>2485.283781</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Basic chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>2018</v>
+      </c>
+      <c r="C36">
+        <v>2424.901397</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Basic chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>2024</v>
+      </c>
+      <c r="C37">
+        <v>2402.340163</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Basic chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>2018</v>
+      </c>
+      <c r="C38">
+        <v>2383.280989</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Fuel oils</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>2017</v>
+      </c>
+      <c r="C39">
+        <v>2376.516354</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Fuel oils</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>2021</v>
+      </c>
+      <c r="C40">
+        <v>2347.830848</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Basic chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>2019</v>
+      </c>
+      <c r="C41">
+        <v>2335.989881</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Basic chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>2023</v>
+      </c>
+      <c r="C42">
+        <v>2322.60127</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Basic chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>2019</v>
+      </c>
+      <c r="C43">
+        <v>2299.568371</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Fuel oils</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>2024</v>
+      </c>
+      <c r="C44">
+        <v>2223.34799</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Wood prods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>2020</v>
+      </c>
+      <c r="C45">
+        <v>2218.217662</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Basic chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B46">
+        <v>2024</v>
+      </c>
+      <c r="C46">
+        <v>2206.370308</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Fuel oils</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>2017</v>
+      </c>
+      <c r="C47">
+        <v>2195.577746</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Wood prods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>2022</v>
+      </c>
+      <c r="C48">
+        <v>2187.594263</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Fuel oils</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>2022</v>
+      </c>
+      <c r="C49">
+        <v>2187.459833</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Basic chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>2023</v>
+      </c>
+      <c r="C50">
+        <v>2150.96774</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Fuel oils</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>2019</v>
+      </c>
+      <c r="C51">
+        <v>2108.950091</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Wood prods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>2018</v>
+      </c>
+      <c r="C52">
+        <v>2104.256587</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Wood prods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>2020</v>
+      </c>
+      <c r="C53">
+        <v>2046.124892</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Wood prods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>2021</v>
+      </c>
+      <c r="C54">
+        <v>2045.085523</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Wood prods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>2019</v>
+      </c>
+      <c r="C55">
+        <v>2008.397315</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Plastics/rubber</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>2022</v>
+      </c>
+      <c r="C56">
+        <v>1994.848061</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Wood prods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>2018</v>
+      </c>
+      <c r="C57">
+        <v>1992.742052</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Plastics/rubber</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>2017</v>
+      </c>
+      <c r="C58">
+        <v>1963.954715</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Plastics/rubber</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B59">
+        <v>2020</v>
+      </c>
+      <c r="C59">
+        <v>1949.797165</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Plastics/rubber</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>2024</v>
+      </c>
+      <c r="C60">
+        <v>1918.191956</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Plastics/rubber</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>2023</v>
+      </c>
+      <c r="C61">
+        <v>1877.369739</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Wood prods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B62">
+        <v>2022</v>
+      </c>
+      <c r="C62">
+        <v>1866.527193</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Plastics/rubber</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B63">
+        <v>2023</v>
+      </c>
+      <c r="C63">
+        <v>1860.23789</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Plastics/rubber</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B64">
+        <v>2023</v>
+      </c>
+      <c r="C64">
+        <v>1847.323395</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Gasoline</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B65">
+        <v>2021</v>
+      </c>
+      <c r="C65">
+        <v>1819.936603</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Fuel oils</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B66">
+        <v>2021</v>
+      </c>
+      <c r="C66">
+        <v>1785.663404</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Plastics/rubber</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B67">
+        <v>2018</v>
+      </c>
+      <c r="C67">
+        <v>1782.028308</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Newsprint/paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B68">
+        <v>2020</v>
+      </c>
+      <c r="C68">
+        <v>1764.738273</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Fuel oils</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B69">
+        <v>2019</v>
+      </c>
+      <c r="C69">
+        <v>1727.093043</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Gasoline</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B70">
+        <v>2017</v>
+      </c>
+      <c r="C70">
         <v>1726.356728</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Gasoline</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B71">
+        <v>2017</v>
+      </c>
+      <c r="C71">
+        <v>1696.458054</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Newsprint/paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B72">
+        <v>2021</v>
+      </c>
+      <c r="C72">
+        <v>1686.023175</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Newsprint/paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B73">
+        <v>2020</v>
+      </c>
+      <c r="C73">
+        <v>1683.045658</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Newsprint/paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B74">
+        <v>2019</v>
+      </c>
+      <c r="C74">
+        <v>1679.838658</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Newsprint/paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B75">
+        <v>2022</v>
+      </c>
+      <c r="C75">
+        <v>1676.595907</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Newsprint/paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B76">
+        <v>2018</v>
+      </c>
+      <c r="C76">
+        <v>1673.140786</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Gasoline</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B77">
+        <v>2021</v>
+      </c>
+      <c r="C77">
+        <v>1665.392208</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Gasoline</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B78">
+        <v>2022</v>
+      </c>
+      <c r="C78">
+        <v>1632.634117</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Gasoline</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B79">
+        <v>2023</v>
+      </c>
+      <c r="C79">
+        <v>1501.321719</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Newsprint/paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B80">
+        <v>2024</v>
+      </c>
+      <c r="C80">
+        <v>1471.010068</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Newsprint/paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B81">
+        <v>2020</v>
+      </c>
+      <c r="C81">
+        <v>1443.037455</v>
+      </c>
+      <c r="D81" t="inlineStr">
         <is>
           <t>Gasoline</t>
         </is>
